--- a/output/topology_excel/12023.xlsx
+++ b/output/topology_excel/12023.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,10 +462,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B2" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -484,10 +484,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B3" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -506,10 +506,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -528,10 +528,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -550,10 +550,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="B6" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -572,10 +572,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -594,10 +594,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -616,10 +616,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -638,10 +638,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -663,7 +663,7 @@
         <v>1</v>
       </c>
       <c r="B11" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -674,10 +674,10 @@
         <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>306</v>
+        <v>178</v>
       </c>
       <c r="F11" t="n">
-        <v>233</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12">
@@ -685,7 +685,7 @@
         <v>1</v>
       </c>
       <c r="B12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -696,10 +696,10 @@
         <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>179</v>
+        <v>294</v>
       </c>
       <c r="F12" t="n">
-        <v>31</v>
+        <v>73</v>
       </c>
     </row>
     <row r="13">
@@ -707,7 +707,7 @@
         <v>1</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>122</v>
+        <v>81</v>
       </c>
       <c r="F13" t="n">
         <v>12</v>
@@ -726,10 +726,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -748,10 +748,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -770,10 +770,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -792,10 +792,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -814,10 +814,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -828,18 +828,18 @@
         <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>173</v>
+        <v>221</v>
       </c>
       <c r="F18" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -850,18 +850,18 @@
         <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>184</v>
+        <v>108</v>
       </c>
       <c r="F19" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -872,10 +872,10 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>226</v>
+        <v>184</v>
       </c>
       <c r="F20" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21">
@@ -883,7 +883,7 @@
         <v>6</v>
       </c>
       <c r="B21" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -894,18 +894,18 @@
         <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>108</v>
+        <v>241</v>
       </c>
       <c r="F21" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B22" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -916,10 +916,10 @@
         <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>241</v>
+        <v>229</v>
       </c>
       <c r="F22" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
     </row>
     <row r="23">
@@ -927,7 +927,7 @@
         <v>7</v>
       </c>
       <c r="B23" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -938,18 +938,18 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>229</v>
+        <v>179</v>
       </c>
       <c r="F23" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
+        <v>7</v>
+      </c>
+      <c r="B24" t="n">
         <v>10</v>
-      </c>
-      <c r="B24" t="n">
-        <v>11</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B25" t="n">
         <v>12</v>
@@ -986,6 +986,116 @@
       </c>
       <c r="F25" t="n">
         <v>28</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>8</v>
+      </c>
+      <c r="B26" t="n">
+        <v>10</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" t="n">
+        <v>122</v>
+      </c>
+      <c r="F26" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>9</v>
+      </c>
+      <c r="B27" t="n">
+        <v>14</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" t="n">
+        <v>173</v>
+      </c>
+      <c r="F27" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>11</v>
+      </c>
+      <c r="B28" t="n">
+        <v>13</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" t="n">
+        <v>226</v>
+      </c>
+      <c r="F28" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>1</v>
+      </c>
+      <c r="B29" t="n">
+        <v>2</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" t="n">
+        <v>228</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>2</v>
+      </c>
+      <c r="B30" t="n">
+        <v>8</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" t="n">
+        <v>124</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/topology_excel/12023.xlsx
+++ b/output/topology_excel/12023.xlsx
@@ -451,12 +451,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Length</t>
+          <t>Length_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Width</t>
+          <t>Width_1</t>
         </is>
       </c>
     </row>
@@ -699,7 +699,7 @@
         <v>294</v>
       </c>
       <c r="F12" t="n">
-        <v>73</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13">
@@ -941,7 +941,7 @@
         <v>179</v>
       </c>
       <c r="F23" t="n">
-        <v>31</v>
+        <v>14</v>
       </c>
     </row>
     <row r="24">
